--- a/data/trans_bre/P14B23-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Provincia-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 9,9</t>
+          <t>2,42; 10,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 12,89</t>
+          <t>4,14; 13,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,09</t>
+          <t>0,85; 5,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,41; 544,35</t>
+          <t>42,26; 598,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,0; 1092,81</t>
+          <t>83,76; 1057,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,78; 888,34</t>
+          <t>7,46; 796,19</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 10,56</t>
+          <t>3,86; 10,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,82</t>
+          <t>2,96; 8,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,23</t>
+          <t>3,62; 9,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,5; 565,89</t>
+          <t>69,79; 545,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,3; 534,49</t>
+          <t>77,02; 524,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,92; 352,81</t>
+          <t>61,75; 370,44</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,64</t>
+          <t>0,04; 6,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,41</t>
+          <t>2,07; 7,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 3,79</t>
+          <t>-3,0; 3,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 385,9</t>
+          <t>-3,17; 417,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,14; 2487,66</t>
+          <t>61,89; 2158,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 98,74</t>
+          <t>-37,87; 89,32</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 11,33</t>
+          <t>5,41; 11,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,18</t>
+          <t>0,72; 5,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 5,26</t>
+          <t>-2,85; 5,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308,39; —</t>
+          <t>251,97; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,47; 1042,76</t>
+          <t>10,62; 907,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 151,56</t>
+          <t>-33,75; 147,72</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 19,02</t>
+          <t>7,7; 18,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,16</t>
+          <t>-1,45; 8,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,57</t>
+          <t>-0,33; 4,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121,3; 1241,56</t>
+          <t>118,96; 1100,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 290,62</t>
+          <t>-24,4; 265,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 945,96</t>
+          <t>-18,08; 1098,81</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,99</t>
+          <t>1,69; 9,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,19</t>
+          <t>5,71; 13,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,77</t>
+          <t>-1,98; 4,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,21; 498,18</t>
+          <t>22,39; 494,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>173,38; 3605,17</t>
+          <t>214,6; 3742,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 121,15</t>
+          <t>-26,31; 133,02</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,68</t>
+          <t>1,27; 5,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,06</t>
+          <t>1,43; 5,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 6,36</t>
+          <t>-1,83; 6,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,57; 330,36</t>
+          <t>28,98; 308,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42,04; 968,69</t>
+          <t>51,79; 1036,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 158,45</t>
+          <t>-26,47; 164,39</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,14</t>
+          <t>1,98; 6,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,29</t>
+          <t>2,17; 6,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,36</t>
+          <t>3,34; 7,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,63; 537,71</t>
+          <t>67,9; 559,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>69,59; 410,5</t>
+          <t>62,36; 393,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>108,64; 765,57</t>
+          <t>112,93; 772,62</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,65</t>
+          <t>4,44; 6,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1284,22 +1284,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,74</t>
+          <t>2,09; 4,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>149,08; 326,82</t>
+          <t>149,52; 324,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>158,33; 353,73</t>
+          <t>156,58; 344,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,83; 154,67</t>
+          <t>51,33; 159,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P14B23-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>198,96%</t>
+          <t>224,94%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 10,54</t>
+          <t>2,38; 10,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 13,33</t>
+          <t>4,37; 12,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,14</t>
+          <t>1,17; 5,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,26; 598,45</t>
+          <t>43,46; 570,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,76; 1057,19</t>
+          <t>77,3; 1000,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 796,19</t>
+          <t>31,37; 870,92</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>164,82%</t>
+          <t>168,96%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,67</t>
+          <t>3,8; 10,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,68</t>
+          <t>2,97; 8,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,37</t>
+          <t>3,96; 9,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,79; 545,98</t>
+          <t>58,98; 653,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,02; 524,15</t>
+          <t>79,32; 534,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,75; 370,44</t>
+          <t>62,19; 382,85</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,76</t>
+          <t>0,06; 6,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,43</t>
+          <t>1,93; 7,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 3,47</t>
+          <t>-2,24; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 417,01</t>
+          <t>-5,65; 448,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,89; 2158,47</t>
+          <t>69,79; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 89,32</t>
+          <t>-30,49; 100,05</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>3,9</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 11,39</t>
+          <t>5,26; 11,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,64</t>
+          <t>0,96; 5,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,47</t>
+          <t>0,29; 7,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>251,97; —</t>
+          <t>276,69; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 907,17</t>
+          <t>29,36; 963,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 147,72</t>
+          <t>1,02; 248,02</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>181,87%</t>
+          <t>270,36%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 18,49</t>
+          <t>7,52; 18,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 8,17</t>
+          <t>-1,46; 8,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,73</t>
+          <t>1,17; 5,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118,96; 1100,92</t>
+          <t>119,82; 1216,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 265,61</t>
+          <t>-26,17; 260,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 1098,81</t>
+          <t>36,06; 1429,64</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,24</t>
+          <t>1,8; 9,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 13,07</t>
+          <t>5,12; 12,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,65</t>
+          <t>-1,77; 4,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,39; 494,12</t>
+          <t>30,61; 542,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>214,6; 3742,04</t>
+          <t>165,17; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 133,02</t>
+          <t>-25,02; 132,95</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>5,5</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>111,02%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,48</t>
+          <t>1,01; 5,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,18</t>
+          <t>1,25; 5,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,58</t>
+          <t>2,75; 8,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,98; 308,71</t>
+          <t>27,42; 320,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,79; 1036,99</t>
+          <t>45,93; 912,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 164,39</t>
+          <t>39,47; 223,08</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>4,24</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>260,89%</t>
+          <t>155,95%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,27</t>
+          <t>2,43; 6,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,4</t>
+          <t>2,37; 6,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,16</t>
+          <t>2,45; 6,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67,9; 559,83</t>
+          <t>75,41; 539,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,36; 393,73</t>
+          <t>73,89; 430,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>112,93; 772,62</t>
+          <t>62,05; 315,25</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>109,27%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,66</t>
+          <t>4,48; 6,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,73</t>
+          <t>3,79; 5,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,79</t>
+          <t>3,1; 5,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>149,52; 324,38</t>
+          <t>149,19; 317,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>156,58; 344,64</t>
+          <t>164,33; 345,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,33; 159,68</t>
+          <t>69,2; 156,78</t>
         </is>
       </c>
     </row>
